--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N92_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N92_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.088974260994958</v>
+        <v>1.476958317411681</v>
       </c>
       <c r="D2" t="n">
-        <v>8.751220916041806</v>
+        <v>1.422073398856794</v>
       </c>
       <c r="E2" t="n">
-        <v>14.41733225465184</v>
+        <v>2.342816491380924</v>
       </c>
       <c r="F2" t="n">
-        <v>11.10907560901493</v>
+        <v>1.805224786464926</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.58801044693507</v>
+        <v>4.808051697626948</v>
       </c>
       <c r="D3" t="n">
-        <v>20.92290375762932</v>
+        <v>3.399971860614765</v>
       </c>
       <c r="E3" t="n">
-        <v>14.41733225465184</v>
+        <v>2.342816491380924</v>
       </c>
       <c r="F3" t="n">
-        <v>11.10907560901493</v>
+        <v>1.805224786464926</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.26646198667388</v>
+        <v>8.005800072834505</v>
       </c>
       <c r="D4" t="n">
-        <v>38.16561972049388</v>
+        <v>6.201913204580255</v>
       </c>
       <c r="E4" t="n">
-        <v>14.41733225465184</v>
+        <v>2.342816491380924</v>
       </c>
       <c r="F4" t="n">
-        <v>11.10907560901493</v>
+        <v>1.805224786464926</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.63288728367873</v>
+        <v>3.840344183597793</v>
       </c>
       <c r="D5" t="n">
-        <v>13.91405898291266</v>
+        <v>2.261034584723308</v>
       </c>
       <c r="E5" t="n">
-        <v>14.41733225465184</v>
+        <v>2.342816491380924</v>
       </c>
       <c r="F5" t="n">
-        <v>11.10907560901493</v>
+        <v>1.805224786464926</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
